--- a/smart_pantry_manager/data/pantry_omnia.xlsx
+++ b/smart_pantry_manager/data/pantry_omnia.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,11 +616,37 @@
           <t>count</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="F7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>45983</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
